--- a/mobile/Test Results/Excel/Failed_Test_Cases.xlsx
+++ b/mobile/Test Results/Excel/Failed_Test_Cases.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,267 +424,52 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Test Name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Execution Time (ms)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Actual Result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>TC_AUTHZ_005</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Authorization</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Verify Authorization - Execution Scenario #5</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>P1-CRITICAL</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>65</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>App Launched, Permissions Granted</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Authorization operates within specifications</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>AssertionError: Element verification timed out after 5000ms</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>TC_NAV_002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Navigation</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Verify Navigation - Execution Scenario #2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>P1-CRITICAL</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>59</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>App Launched, Permissions Granted</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Navigation operates within specifications</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>AssertionError: Element verification timed out after 5000ms</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>TC_FORM_038</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Forms</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Verify Forms - Execution Scenario #38</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>P3-MEDIUM</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>91</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>App Launched, Permissions Granted</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Forms operates within specifications</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>AssertionError: Element verification timed out after 5000ms</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TC_SRCH_016</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Search</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Verify Search - Execution Scenario #16</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>P3-MEDIUM</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>117</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>App Launched, Permissions Granted</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Search operates within specifications</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>AssertionError: Element verification timed out after 5000ms</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>TC_NOTIF_020</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Notifications</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Verify Notifications - Execution Scenario #20</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>P3-MEDIUM</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>35</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>App Launched, Permissions Granted</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Notifications operates within specifications</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>AssertionError: Element verification timed out after 5000ms</t>
         </is>
       </c>
     </row>
